--- a/google play/reports/eda_section_c_workbook.xlsx
+++ b/google play/reports/eda_section_c_workbook.xlsx
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D50"/>
+  <dimension ref="A1:D49"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -444,7 +444,7 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>10169</v>
+        <v>10940</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -462,7 +462,7 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>558</v>
+        <v>501</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -480,7 +480,7 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>309</v>
+        <v>493</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -494,15 +494,15 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Italian</t>
+          <t>Norwegian</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>256</v>
+        <v>338</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>it</t>
+          <t>no</t>
         </is>
       </c>
     </row>
@@ -516,7 +516,7 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>232</v>
+        <v>333</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -530,15 +530,15 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Norwegian</t>
+          <t>Spanish</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>193</v>
+        <v>311</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>es</t>
         </is>
       </c>
     </row>
@@ -548,15 +548,15 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>French</t>
+          <t>Slovenian</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>188</v>
+        <v>309</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>fr</t>
+          <t>sl</t>
         </is>
       </c>
     </row>
@@ -566,15 +566,15 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Catalan</t>
+          <t>Polish</t>
         </is>
       </c>
       <c r="C9" t="n">
-        <v>186</v>
+        <v>267</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>ca</t>
+          <t>pl</t>
         </is>
       </c>
     </row>
@@ -584,15 +584,15 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Indonesian</t>
+          <t>Catalan</t>
         </is>
       </c>
       <c r="C10" t="n">
-        <v>159</v>
+        <v>222</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>id</t>
+          <t>ca</t>
         </is>
       </c>
     </row>
@@ -602,15 +602,15 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Tagalog</t>
+          <t>Danish</t>
         </is>
       </c>
       <c r="C11" t="n">
-        <v>138</v>
+        <v>192</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>tl</t>
+          <t>da</t>
         </is>
       </c>
     </row>
@@ -620,15 +620,15 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Slovenian</t>
+          <t>Albanian</t>
         </is>
       </c>
       <c r="C12" t="n">
-        <v>125</v>
+        <v>171</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>sl</t>
+          <t>sq</t>
         </is>
       </c>
     </row>
@@ -638,15 +638,15 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Polish</t>
+          <t>Italian</t>
         </is>
       </c>
       <c r="C13" t="n">
-        <v>119</v>
+        <v>153</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>pl</t>
+          <t>it</t>
         </is>
       </c>
     </row>
@@ -660,7 +660,7 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>108</v>
+        <v>140</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -674,15 +674,15 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Czech</t>
+          <t>Tagalog</t>
         </is>
       </c>
       <c r="C15" t="n">
-        <v>108</v>
+        <v>133</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>cs</t>
+          <t>tl</t>
         </is>
       </c>
     </row>
@@ -692,15 +692,15 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Dutch</t>
+          <t>French</t>
         </is>
       </c>
       <c r="C16" t="n">
-        <v>81</v>
+        <v>112</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>nl</t>
+          <t>fr</t>
         </is>
       </c>
     </row>
@@ -710,15 +710,15 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Swahili</t>
+          <t>Indonesian</t>
         </is>
       </c>
       <c r="C17" t="n">
-        <v>79</v>
+        <v>91</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>sw</t>
+          <t>id</t>
         </is>
       </c>
     </row>
@@ -728,7 +728,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Albanian</t>
+          <t>Croatian</t>
         </is>
       </c>
       <c r="C18" t="n">
@@ -736,7 +736,7 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>sq</t>
+          <t>hr</t>
         </is>
       </c>
     </row>
@@ -746,15 +746,15 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Danish</t>
+          <t>Swahili</t>
         </is>
       </c>
       <c r="C19" t="n">
-        <v>69</v>
+        <v>64</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>da</t>
+          <t>sw</t>
         </is>
       </c>
     </row>
@@ -764,15 +764,15 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Bengali</t>
+          <t>Dutch</t>
         </is>
       </c>
       <c r="C20" t="n">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>bn</t>
+          <t>nl</t>
         </is>
       </c>
     </row>
@@ -782,15 +782,15 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Arabic</t>
+          <t>Czech</t>
         </is>
       </c>
       <c r="C21" t="n">
-        <v>62</v>
+        <v>52</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>ar</t>
+          <t>cs</t>
         </is>
       </c>
     </row>
@@ -800,15 +800,15 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Estonian</t>
+          <t>Unknown (undetected or too short)</t>
         </is>
       </c>
       <c r="C22" t="n">
-        <v>60</v>
+        <v>51</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>et</t>
+          <t>unknown</t>
         </is>
       </c>
     </row>
@@ -818,15 +818,15 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Spanish</t>
+          <t>Estonian</t>
         </is>
       </c>
       <c r="C23" t="n">
-        <v>56</v>
+        <v>50</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>es</t>
+          <t>et</t>
         </is>
       </c>
     </row>
@@ -836,15 +836,15 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Croatian</t>
+          <t>Swedish</t>
         </is>
       </c>
       <c r="C24" t="n">
-        <v>53</v>
+        <v>50</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>hr</t>
+          <t>sv</t>
         </is>
       </c>
     </row>
@@ -854,15 +854,15 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Unknown (undetected or too short)</t>
+          <t>Portuguese</t>
         </is>
       </c>
       <c r="C25" t="n">
-        <v>50</v>
+        <v>25</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>pt</t>
         </is>
       </c>
     </row>
@@ -872,15 +872,15 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Swedish</t>
+          <t>Finnish</t>
         </is>
       </c>
       <c r="C26" t="n">
-        <v>48</v>
+        <v>21</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>sv</t>
+          <t>fi</t>
         </is>
       </c>
     </row>
@@ -890,15 +890,15 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Portuguese</t>
+          <t>Hungarian</t>
         </is>
       </c>
       <c r="C27" t="n">
-        <v>40</v>
+        <v>21</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>pt</t>
+          <t>hu</t>
         </is>
       </c>
     </row>
@@ -908,15 +908,15 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Russian</t>
+          <t>Slovak</t>
         </is>
       </c>
       <c r="C28" t="n">
-        <v>38</v>
+        <v>18</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>ru</t>
+          <t>sk</t>
         </is>
       </c>
     </row>
@@ -926,15 +926,15 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Finnish</t>
+          <t>German</t>
         </is>
       </c>
       <c r="C29" t="n">
-        <v>29</v>
+        <v>17</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>fi</t>
+          <t>de</t>
         </is>
       </c>
     </row>
@@ -948,7 +948,7 @@
         </is>
       </c>
       <c r="C30" t="n">
-        <v>24</v>
+        <v>16</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -962,15 +962,15 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Slovak</t>
+          <t>Arabic</t>
         </is>
       </c>
       <c r="C31" t="n">
-        <v>24</v>
+        <v>11</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>sk</t>
+          <t>ar</t>
         </is>
       </c>
     </row>
@@ -984,7 +984,7 @@
         </is>
       </c>
       <c r="C32" t="n">
-        <v>17</v>
+        <v>8</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -998,15 +998,15 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Hindi</t>
+          <t>Lithuanian</t>
         </is>
       </c>
       <c r="C33" t="n">
-        <v>14</v>
+        <v>6</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>hi</t>
+          <t>lt</t>
         </is>
       </c>
     </row>
@@ -1016,15 +1016,15 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Persian (Farsi)</t>
+          <t>Bengali</t>
         </is>
       </c>
       <c r="C34" t="n">
-        <v>13</v>
+        <v>5</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>fa</t>
+          <t>bn</t>
         </is>
       </c>
     </row>
@@ -1034,15 +1034,15 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Hungarian</t>
+          <t>Hindi</t>
         </is>
       </c>
       <c r="C35" t="n">
-        <v>12</v>
+        <v>5</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>hu</t>
+          <t>hi</t>
         </is>
       </c>
     </row>
@@ -1052,15 +1052,15 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>German</t>
+          <t>Persian (Farsi)</t>
         </is>
       </c>
       <c r="C36" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>de</t>
+          <t>fa</t>
         </is>
       </c>
     </row>
@@ -1070,15 +1070,15 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Lithuanian</t>
+          <t>Marathi</t>
         </is>
       </c>
       <c r="C37" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>lt</t>
+          <t>mr</t>
         </is>
       </c>
     </row>
@@ -1088,15 +1088,15 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Urdu</t>
+          <t>Telugu</t>
         </is>
       </c>
       <c r="C38" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>ur</t>
+          <t>te</t>
         </is>
       </c>
     </row>
@@ -1106,15 +1106,15 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Thai</t>
+          <t>Vietnamese</t>
         </is>
       </c>
       <c r="C39" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>th</t>
+          <t>vi</t>
         </is>
       </c>
     </row>
@@ -1124,15 +1124,15 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Chinese (Simplified)</t>
+          <t>Kannada</t>
         </is>
       </c>
       <c r="C40" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>zh-cn</t>
+          <t>kn</t>
         </is>
       </c>
     </row>
@@ -1142,15 +1142,15 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Vietnamese</t>
+          <t>Russian</t>
         </is>
       </c>
       <c r="C41" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>vi</t>
+          <t>ru</t>
         </is>
       </c>
     </row>
@@ -1160,15 +1160,15 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Tamil</t>
+          <t>Urdu</t>
         </is>
       </c>
       <c r="C42" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>ta</t>
+          <t>ur</t>
         </is>
       </c>
     </row>
@@ -1178,7 +1178,7 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Ukrainian</t>
+          <t>Chinese (Simplified)</t>
         </is>
       </c>
       <c r="C43" t="n">
@@ -1186,7 +1186,7 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>uk</t>
+          <t>zh-cn</t>
         </is>
       </c>
     </row>
@@ -1196,15 +1196,15 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Korean</t>
+          <t>Thai</t>
         </is>
       </c>
       <c r="C44" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>ko</t>
+          <t>th</t>
         </is>
       </c>
     </row>
@@ -1232,7 +1232,7 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Other language (el)</t>
+          <t>Other language (ml)</t>
         </is>
       </c>
       <c r="C46" t="n">
@@ -1240,7 +1240,7 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>el</t>
+          <t>ml</t>
         </is>
       </c>
     </row>
@@ -1250,7 +1250,7 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Other language (ml)</t>
+          <t>Ukrainian</t>
         </is>
       </c>
       <c r="C47" t="n">
@@ -1258,7 +1258,7 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>ml</t>
+          <t>uk</t>
         </is>
       </c>
     </row>
@@ -1268,7 +1268,7 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Marathi</t>
+          <t>Tamil</t>
         </is>
       </c>
       <c r="C48" t="n">
@@ -1276,7 +1276,7 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>mr</t>
+          <t>ta</t>
         </is>
       </c>
     </row>
@@ -1286,7 +1286,7 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Macedonian</t>
+          <t>Other language (gu)</t>
         </is>
       </c>
       <c r="C49" t="n">
@@ -1294,25 +1294,7 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>mk</t>
-        </is>
-      </c>
-    </row>
-    <row r="50">
-      <c r="A50" t="n">
-        <v>48</v>
-      </c>
-      <c r="B50" t="inlineStr">
-        <is>
-          <t>Kannada</t>
-        </is>
-      </c>
-      <c r="C50" t="n">
-        <v>1</v>
-      </c>
-      <c r="D50" t="inlineStr">
-        <is>
-          <t>kn</t>
+          <t>gu</t>
         </is>
       </c>
     </row>
@@ -1362,7 +1344,7 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>0.736564</v>
+        <v>0.7155</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -1370,7 +1352,7 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>13806</v>
+        <v>15290</v>
       </c>
     </row>
     <row r="3">
@@ -1383,7 +1365,7 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>15405</v>
+        <v>16800</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -1402,7 +1384,7 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>13806</v>
+        <v>15290</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1421,7 +1403,7 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>0.7366</v>
+        <v>0.7155</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1440,7 +1422,7 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>10169</v>
+        <v>10940</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
